--- a/A小区1单元.xlsx
+++ b/A小区1单元.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="128">
   <si>
     <t>计费号</t>
   </si>
@@ -34,6 +34,12 @@
     <t>录入月份</t>
   </si>
   <si>
+    <t>2023-06</t>
+  </si>
+  <si>
+    <t>2023-08</t>
+  </si>
+  <si>
     <t>442667</t>
   </si>
   <si>
@@ -44,9 +50,6 @@
   </si>
   <si>
     <t>测试-101</t>
-  </si>
-  <si>
-    <t>2023-08</t>
   </si>
   <si>
     <t>442668</t>
@@ -1434,8 +1437,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" outlineLevelCol="7"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="8.14285714285714" customWidth="1"/>
@@ -1446,7 +1449,7 @@
     <col min="7" max="7" width="5.42857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1467,19 +1470,25 @@
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
@@ -1487,21 +1496,27 @@
         <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I2" s="10">
+        <v>17</v>
+      </c>
+      <c r="J2" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
@@ -1509,21 +1524,27 @@
         <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I3" s="10">
+        <v>15</v>
+      </c>
+      <c r="J3" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="9"/>
@@ -1531,21 +1552,27 @@
         <v>5</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I4" s="10">
+        <v>5</v>
+      </c>
+      <c r="J4" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="9"/>
@@ -1553,21 +1580,27 @@
         <v>13</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I5" s="10">
+        <v>13</v>
+      </c>
+      <c r="J5" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="9"/>
@@ -1575,21 +1608,27 @@
         <v>25</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I6" s="10">
+        <v>25</v>
+      </c>
+      <c r="J6" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="9"/>
@@ -1597,21 +1636,27 @@
         <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I7" s="10">
+        <v>23</v>
+      </c>
+      <c r="J7" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="9"/>
@@ -1619,21 +1664,27 @@
         <v>15</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I8" s="10">
+        <v>15</v>
+      </c>
+      <c r="J8" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="9"/>
@@ -1641,21 +1692,27 @@
         <v>27</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I9" s="10">
+        <v>27</v>
+      </c>
+      <c r="J9" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="9"/>
@@ -1663,21 +1720,27 @@
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:8">
+      <c r="J10" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="9"/>
@@ -1685,21 +1748,27 @@
         <v>22</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I11" s="10">
+        <v>22</v>
+      </c>
+      <c r="J11" s="10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="9"/>
@@ -1707,21 +1776,27 @@
         <v>21</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I12" s="10">
+        <v>21</v>
+      </c>
+      <c r="J12" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:10">
       <c r="A13" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="9"/>
@@ -1729,21 +1804,27 @@
         <v>8</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I13" s="10">
+        <v>8</v>
+      </c>
+      <c r="J13" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:10">
       <c r="A14" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="9"/>
@@ -1751,21 +1832,27 @@
         <v>21</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I14" s="10">
+        <v>21</v>
+      </c>
+      <c r="J14" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:10">
       <c r="A15" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="9"/>
@@ -1773,21 +1860,27 @@
         <v>6</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I15" s="10">
+        <v>6</v>
+      </c>
+      <c r="J15" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:10">
       <c r="A16" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="9"/>
@@ -1795,21 +1888,27 @@
         <v>6</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I16" s="10">
+        <v>6</v>
+      </c>
+      <c r="J16" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:10">
       <c r="A17" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="9"/>
@@ -1817,21 +1916,27 @@
         <v>24</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I17" s="10">
+        <v>24</v>
+      </c>
+      <c r="J17" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:10">
       <c r="A18" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="9"/>
@@ -1839,21 +1944,27 @@
         <v>14</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I18" s="10">
+        <v>14</v>
+      </c>
+      <c r="J18" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:10">
       <c r="A19" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="9"/>
@@ -1861,21 +1972,27 @@
         <v>7</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I19" s="10">
+        <v>7</v>
+      </c>
+      <c r="J19" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:10">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="9"/>
@@ -1883,21 +2000,27 @@
         <v>12</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I20" s="10">
+        <v>12</v>
+      </c>
+      <c r="J20" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:10">
       <c r="A21" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
@@ -1905,21 +2028,27 @@
         <v>6</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I21" s="10">
+        <v>6</v>
+      </c>
+      <c r="J21" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:10">
       <c r="A22" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
@@ -1927,21 +2056,27 @@
         <v>14</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I22" s="10">
+        <v>14</v>
+      </c>
+      <c r="J22" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:10">
       <c r="A23" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
@@ -1949,21 +2084,27 @@
         <v>8</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I23" s="10">
+        <v>8</v>
+      </c>
+      <c r="J23" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:10">
       <c r="A24" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
@@ -1971,21 +2112,27 @@
         <v>11</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I24" s="10">
+        <v>11</v>
+      </c>
+      <c r="J24" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:10">
       <c r="A25" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="9"/>
@@ -1993,21 +2140,27 @@
         <v>28</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I25" s="10">
+        <v>28</v>
+      </c>
+      <c r="J25" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:10">
       <c r="A26" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
@@ -2015,21 +2168,27 @@
         <v>13</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I26" s="10">
+        <v>13</v>
+      </c>
+      <c r="J26" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:10">
       <c r="A27" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
@@ -2037,21 +2196,27 @@
         <v>16</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I27" s="10">
+        <v>16</v>
+      </c>
+      <c r="J27" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:10">
       <c r="A28" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="9"/>
@@ -2059,21 +2224,27 @@
         <v>10</v>
       </c>
       <c r="H28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:8">
+      <c r="J28" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:10">
       <c r="A29" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="9"/>
@@ -2081,21 +2252,27 @@
         <v>10</v>
       </c>
       <c r="H29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" s="10">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:8">
+      <c r="J29" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:10">
       <c r="A30" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="9"/>
@@ -2103,21 +2280,27 @@
         <v>9</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I30" s="10">
+        <v>9</v>
+      </c>
+      <c r="J30" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:10">
       <c r="A31" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="9"/>
@@ -2125,6 +2308,12 @@
         <v>10</v>
       </c>
       <c r="H31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" s="10">
+        <v>10</v>
+      </c>
+      <c r="J31" s="10">
         <v>10</v>
       </c>
     </row>
